--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Vaccinazioni.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Vaccinazioni.xlsx
@@ -148,7 +148,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>n/a</t>
+    <t>Scopri di più</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -808,7 +808,7 @@
     <t>Prenota un appuntamento</t>
   </si>
   <si>
-    <t>Gestire prenotazione</t>
+    <t>Gestisci prenotazione</t>
   </si>
   <si>
     <r>
@@ -828,7 +828,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
